--- a/DateBase/orders/Nha Thu_2026-6-28.xlsx
+++ b/DateBase/orders/Nha Thu_2026-6-28.xlsx
@@ -1167,6 +1167,9 @@
       <c r="G2" t="str">
         <v>01010201051210108510201510554016225101555610510101010510101530101051510810109101651010105105101010551055553355510105105151015</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
